--- a/data/trans_camb/IMC_inf_MED_R3-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R3-Edad-trans_camb.xlsx
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-6.98726641646229</v>
+        <v>-1.142918371920737</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-21.73821845937374</v>
+        <v>-13.2938075357657</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>-4.422473253321457</v>
+        <v>-0.9525489178395963</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-22.72231159725229</v>
+        <v>-19.9261195701431</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-5.660665437380197</v>
+        <v>-1.263140756838271</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-22.30140217894554</v>
+        <v>-16.92866725593477</v>
       </c>
     </row>
     <row r="5">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-28.17386320372909</v>
+        <v>-19.63535668376315</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-39.94539968386236</v>
+        <v>-29.70957079736211</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-21.77269982704022</v>
+        <v>-17.93110031006509</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-39.96653924509658</v>
+        <v>-36.90981655235952</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-19.27404931907295</v>
+        <v>-13.25919344165031</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-35.59780573578415</v>
+        <v>-29.59253067397226</v>
       </c>
     </row>
     <row r="6">
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>12.9466216700337</v>
+        <v>16.17076857653682</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>1.273658253657617</v>
+        <v>9.171038182583992</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>16.05846666492168</v>
+        <v>16.03624983433515</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-0.8949357442141712</v>
+        <v>-0.6524055035920652</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>8.695790475965877</v>
+        <v>12.22474672717121</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>-5.499610638576693</v>
+        <v>-0.2175732583214274</v>
       </c>
     </row>
     <row r="7">
@@ -679,22 +679,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-0.1978834483328146</v>
+        <v>-0.04254207751388374</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.615638988548954</v>
+        <v>-0.4948264062732361</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>-0.1232693645788694</v>
+        <v>-0.02879504456687166</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.6333480728804239</v>
+        <v>-0.6023559423787034</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.158935382729568</v>
+        <v>-0.041765819597082</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.6261599329490046</v>
+        <v>-0.5597473272892959</v>
       </c>
     </row>
     <row r="8">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.6315780336895455</v>
+        <v>-0.5467741327544542</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-0.9286050678642636</v>
+        <v>-0.9192581931075028</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0.5066545640630368</v>
+        <v>-0.4489859806504684</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.9478436569106741</v>
+        <v>-0.9456986554162091</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.4583930653063722</v>
+        <v>-0.3881870634592059</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.864864543345087</v>
+        <v>-0.8485225559420673</v>
       </c>
     </row>
     <row r="9">
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.6074426670098118</v>
+        <v>0.9103506449461826</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.1378145089674082</v>
+        <v>0.5474093343596026</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.7103622239018668</v>
+        <v>0.6763768797367441</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.1705858373858018</v>
+        <v>0.1300107912178074</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.3006118853537095</v>
+        <v>0.497316173308889</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>-0.1610977350462864</v>
+        <v>0.02291641363893885</v>
       </c>
     </row>
     <row r="10">
@@ -761,22 +761,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-15.27884520905277</v>
+        <v>-13.47142935207149</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-11.22497684073303</v>
+        <v>-7.034825409344004</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-10.13275321822696</v>
+        <v>-10.40275077951821</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-6.443105317639858</v>
+        <v>-4.318876485755113</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-12.69069150177444</v>
+        <v>-11.86687459156346</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-8.589985666267902</v>
+        <v>-5.472916807839622</v>
       </c>
     </row>
     <row r="11">
@@ -787,22 +787,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-23.37810067227052</v>
+        <v>-20.33330863760871</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-21.30588576623513</v>
+        <v>-16.03065855933086</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-17.45889798020818</v>
+        <v>-17.1673276705243</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-15.92605335944985</v>
+        <v>-13.2281669492941</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-17.96089891309247</v>
+        <v>-16.589864769068</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-16.48228573606823</v>
+        <v>-12.16968433481509</v>
       </c>
     </row>
     <row r="12">
@@ -813,22 +813,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>-7.285067942315433</v>
+        <v>-6.567213840946716</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>-0.24647351824285</v>
+        <v>4.606701102358012</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-2.547216652919422</v>
+        <v>-3.21611060294552</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>4.872470364571535</v>
+        <v>6.100918107677741</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-7.401520349823068</v>
+        <v>-7.145636241683972</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-0.9359517587149915</v>
+        <v>1.802528242127906</v>
       </c>
     </row>
     <row r="13">
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>-0.3461955918557164</v>
+        <v>-0.342879987286658</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.2543410478850713</v>
+        <v>-0.1790530747614264</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>-0.3134322011814081</v>
+        <v>-0.3495309401950534</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.1993018717280935</v>
+        <v>-0.1451136329848909</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.3293532145654192</v>
+        <v>-0.3408292240373712</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.2229302786109512</v>
+        <v>-0.157187975186254</v>
       </c>
     </row>
     <row r="14">
@@ -865,22 +865,22 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-0.4779158216200809</v>
+        <v>-0.4695159193064946</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-0.461343832176594</v>
+        <v>-0.3869994741616594</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-0.4838723380624665</v>
+        <v>-0.5153038014497646</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.4686000483335913</v>
+        <v>-0.4218795922458594</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.4342262614102247</v>
+        <v>-0.4404563082747007</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.4046311334659797</v>
+        <v>-0.3332343407072134</v>
       </c>
     </row>
     <row r="15">
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>-0.1660875074919123</v>
+        <v>-0.1771341455525686</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>-0.004103656360784845</v>
+        <v>0.1326404717838682</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>-0.08605394811740209</v>
+        <v>-0.1223152622100419</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0.165937320491351</v>
+        <v>0.2257100464176043</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.2009321482907864</v>
+        <v>-0.2203570093967284</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.02606825590801666</v>
+        <v>0.06061348334052228</v>
       </c>
     </row>
     <row r="16">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.9884232287514699</v>
+        <v>-0.2446992223440303</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.1620211435942709</v>
+        <v>-1.080483597571913</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-12.76474196382352</v>
+        <v>-12.1615613205892</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-10.09020817435107</v>
+        <v>-8.660630202803702</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-5.910674091893458</v>
+        <v>-6.272899246488881</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-4.031222452719375</v>
+        <v>-4.17333442854235</v>
       </c>
     </row>
     <row r="17">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-7.25291220521202</v>
+        <v>-7.254988800070366</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-8.909354010608615</v>
+        <v>-10.01418022766627</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-19.99478744207973</v>
+        <v>-19.42204463302188</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-17.92369051177741</v>
+        <v>-16.38088232001529</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-10.78315946928597</v>
+        <v>-11.32513653151669</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-11.24590425982037</v>
+        <v>-10.12942750860831</v>
       </c>
     </row>
     <row r="18">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>9.394532245804935</v>
+        <v>7.990389917736114</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>10.58311438799696</v>
+        <v>8.686591711276549</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>-6.244482612448702</v>
+        <v>-6.205187739939292</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.6513294046453417</v>
+        <v>0.750277007215215</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.129284502875168</v>
+        <v>-0.7277794396811992</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>3.103256817583167</v>
+        <v>2.050016295916584</v>
       </c>
     </row>
     <row r="19">
@@ -999,22 +999,22 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.04007336871632236</v>
+        <v>-0.0100516839550062</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>0.006568778270513478</v>
+        <v>-0.04438379303916057</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-0.5756637018955442</v>
+        <v>-0.5676456588174247</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.4550477093078452</v>
+        <v>-0.4042383216800997</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.2522807354833253</v>
+        <v>-0.2740264612507139</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.1720615532945324</v>
+        <v>-0.1823086933381463</v>
       </c>
     </row>
     <row r="20">
@@ -1025,22 +1025,22 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>-0.2522108531311728</v>
+        <v>-0.2591492949099666</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-0.3143662664199117</v>
+        <v>-0.3625356701644784</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-0.7463731575313444</v>
+        <v>-0.7399017990760642</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.7078527336977888</v>
+        <v>-0.6729685882421735</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.4164999977191381</v>
+        <v>-0.4402090879389239</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.4224557069239932</v>
+        <v>-0.4050927529174834</v>
       </c>
     </row>
     <row r="21">
@@ -1051,22 +1051,22 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>0.4579080547371901</v>
+        <v>0.415732636928106</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>0.5072593167635389</v>
+        <v>0.4019864604867227</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>-0.3189888464371665</v>
+        <v>-0.3284289317656701</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>-0.00319534398777925</v>
+        <v>0.06688759692791178</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.004912060868393778</v>
+        <v>-0.03744776124079667</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.1476129871298522</v>
+        <v>0.09474572714733399</v>
       </c>
     </row>
     <row r="22">
@@ -1081,22 +1081,22 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-2.259626329950607</v>
+        <v>-0.4540142006648915</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>1.358612695302307</v>
+        <v>1.640951607498148</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.3698915214922341</v>
+        <v>-1.202869226700946</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-1.069643127129405</v>
+        <v>-2.010260611368956</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.9661551535947437</v>
+        <v>-0.8150173383407635</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0.3618482340749116</v>
+        <v>0.05540895915579491</v>
       </c>
     </row>
     <row r="23">
@@ -1107,22 +1107,22 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-7.016588319876209</v>
+        <v>-4.774269487742351</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-4.294377843055507</v>
+        <v>-3.483807711300045</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-4.019637946796424</v>
+        <v>-5.231043283736409</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-4.941148891684223</v>
+        <v>-5.999603048238527</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-4.285402477264184</v>
+        <v>-4.07735200864289</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-3.825448241714217</v>
+        <v>-3.387095362342429</v>
       </c>
     </row>
     <row r="24">
@@ -1133,22 +1133,22 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>2.546489802481556</v>
+        <v>4.078540159348351</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>7.960841254400504</v>
+        <v>8.356950261524551</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>4.842295994605883</v>
+        <v>3.179187317773255</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>4.342387712086112</v>
+        <v>3.25899561004356</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>2.107049663444447</v>
+        <v>2.161549232338769</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>4.654474492804423</v>
+        <v>4.135444752381369</v>
       </c>
     </row>
     <row r="25">
@@ -1159,22 +1159,22 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>-0.2795624435531814</v>
+        <v>-0.06136020703272844</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>0.168088448920397</v>
+        <v>0.2217752885687681</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>0.0695332858070947</v>
+        <v>-0.1953569043069433</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.2010746312060169</v>
+        <v>-0.3264846096065762</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.1436941984617314</v>
+        <v>-0.1200822388326431</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.0538169172588164</v>
+        <v>0.008163791803938791</v>
       </c>
     </row>
     <row r="26">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>-0.6856447681129403</v>
+        <v>-0.5154469844540314</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>-0.4410849827701775</v>
+        <v>-0.4105233070393009</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-0.558785973776258</v>
+        <v>-0.6585205483079075</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-0.7307495862415421</v>
+        <v>-0.786631611558969</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.5071336394063207</v>
+        <v>-0.4786636571746021</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.5020873566456914</v>
+        <v>-0.4211298715185016</v>
       </c>
     </row>
     <row r="27">
@@ -1211,22 +1211,22 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>0.5287102153148039</v>
+        <v>0.8493266760756866</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>1.287668385573334</v>
+        <v>1.527215700240529</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>1.729712064339471</v>
+        <v>0.8625563832944478</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>1.527021558299495</v>
+        <v>0.9451999602429896</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.428911931265221</v>
+        <v>0.4243325098797721</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>0.8385043599226608</v>
+        <v>0.7631643948608152</v>
       </c>
     </row>
     <row r="28">
@@ -1241,22 +1241,22 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>-6.598248158520778</v>
+        <v>-5.583151166360387</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>-8.113762417935517</v>
+        <v>-6.68556263533474</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>-7.893069262130526</v>
+        <v>-8.197869741194271</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-10.11183936014612</v>
+        <v>-9.143744298366643</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-7.176371486902122</v>
+        <v>-6.782909945409507</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>-8.722738741024012</v>
+        <v>-7.573650100786969</v>
       </c>
     </row>
     <row r="29">
@@ -1267,22 +1267,22 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>-11.03258844248462</v>
+        <v>-9.284304315577327</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>-12.91320251250455</v>
+        <v>-11.84553850774274</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-11.27482969603891</v>
+        <v>-11.71637426954293</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>-14.10600311865373</v>
+        <v>-12.98082423588392</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-9.892999748091762</v>
+        <v>-9.331034448888031</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>-12.1826609401635</v>
+        <v>-10.70824123917432</v>
       </c>
     </row>
     <row r="30">
@@ -1293,22 +1293,22 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>-2.142384736099197</v>
+        <v>-1.727670538408725</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>-2.543874511370215</v>
+        <v>-1.845889933489961</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>-3.426379899764664</v>
+        <v>-4.734638920651528</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-4.807337501895701</v>
+        <v>-4.459975793351885</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-3.951096404486645</v>
+        <v>-4.039963180515583</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>-5.004738583199533</v>
+        <v>-4.243707485344875</v>
       </c>
     </row>
     <row r="31">
@@ -1319,22 +1319,22 @@
         </is>
       </c>
       <c r="C31" s="6" t="n">
-        <v>-0.2350514343468103</v>
+        <v>-0.2159870972607307</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>-0.2890390674109686</v>
+        <v>-0.2586344564447968</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>-0.3618655677473216</v>
+        <v>-0.3899495765883395</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>-0.4635872775860201</v>
+        <v>-0.4349421654826973</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>-0.2869308769885928</v>
+        <v>-0.2886984772911741</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>-0.3487588513599657</v>
+        <v>-0.3223544568969415</v>
       </c>
     </row>
     <row r="32">
@@ -1345,22 +1345,22 @@
         </is>
       </c>
       <c r="C32" s="6" t="n">
-        <v>-0.354259004094362</v>
+        <v>-0.3396624314896944</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>-0.4393574037103257</v>
+        <v>-0.4281998567625147</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>-0.4813608701542939</v>
+        <v>-0.5075838240134847</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>-0.6060895617186332</v>
+        <v>-0.5883578104932133</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>-0.3768725029847597</v>
+        <v>-0.3794695429892992</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>-0.4610866861073419</v>
+        <v>-0.4351962147731114</v>
       </c>
     </row>
     <row r="33">
@@ -1371,22 +1371,22 @@
         </is>
       </c>
       <c r="C33" s="6" t="n">
-        <v>-0.07647618632731647</v>
+        <v>-0.07210510242710264</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>-0.09703842434576994</v>
+        <v>-0.07156923439645424</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>-0.1825640570666804</v>
+        <v>-0.2474241005013212</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>-0.2439439414312926</v>
+        <v>-0.2333212092101253</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-0.1701161162912276</v>
+        <v>-0.1806509855487162</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-0.2107793357035836</v>
+        <v>-0.1880863014103842</v>
       </c>
     </row>
     <row r="34">
